--- a/artfynd/A 13604-2022 artfynd.xlsx
+++ b/artfynd/A 13604-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13604-2022 artfynd.xlsx
+++ b/artfynd/A 13604-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,134 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121518546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57301</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kittelfjäll Värdshus, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>523530</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7236632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inge Eckert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inge Eckert, Falco Eigner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13604-2022 artfynd.xlsx
+++ b/artfynd/A 13604-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121518546</v>
       </c>
       <c r="B4" t="n">
-        <v>57301</v>
+        <v>57302</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13604-2022 artfynd.xlsx
+++ b/artfynd/A 13604-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121518546</v>
       </c>
       <c r="B4" t="n">
-        <v>57302</v>
+        <v>57303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13604-2022 artfynd.xlsx
+++ b/artfynd/A 13604-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84845966</v>
+        <v>110155299</v>
       </c>
       <c r="B2" t="n">
-        <v>84985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3279</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Maskfingersvamp</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavaria fragilis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Holmsk.:Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kittelfjäll Majvägen, Ås lm</t>
+          <t>Backarna, Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523521.6308276762</v>
+        <v>523366</v>
       </c>
       <c r="R2" t="n">
-        <v>7236773.129129119</v>
+        <v>7237025</v>
       </c>
       <c r="S2" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +771,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan  Olsson</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan  Olsson, Gunilla Kärrfelt</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89755659</v>
+        <v>110155300</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +800,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kittelfjäll, Ås lm</t>
+          <t>Backarna, Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523448.1520471857</v>
+        <v>523366</v>
       </c>
       <c r="R3" t="n">
-        <v>7236515.191478881</v>
+        <v>7237025</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,27 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,36 +887,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121518546</v>
+        <v>110155301</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,53 +914,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102620</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kittelfjäll Värdshus, Ås lm</t>
+          <t>Backarna, Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523530</v>
+        <v>523366</v>
       </c>
       <c r="R4" t="n">
-        <v>7236632</v>
+        <v>7237025</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +975,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2023-06-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +1005,2166 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Inge Eckert</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Inge Eckert, Falco Eigner</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110155302</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backarna, Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>523366</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7237025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110155304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Backarna, Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7237025</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89755391</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523392</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7236491</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89755392</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523376</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7236488</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89755393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523379</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7236496</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89755394</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523374</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7236491</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89755395</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523370</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7236489</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>89755396</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>523367</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7236489</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89755397</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>523365</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7236486</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>89755652</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>523695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7236618</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89755653</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>523621</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7236574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89755654</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>523592</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7236562</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89755655</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>523569</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7236552</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89755656</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>523562</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7236549</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89755657</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>523546</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7236547</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89755658</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>523465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7236518</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89755659</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>523448</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7236515</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>89755660</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>523429</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7236505</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>89755771</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>523375</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7236471</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>89755772</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>523389</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7236471</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering längs väg 1088, Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>sofia nordin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
